--- a/artfynd/A 20593-2024 artfynd.xlsx
+++ b/artfynd/A 20593-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121185794</v>
+        <v>121185854</v>
       </c>
       <c r="B2" t="n">
-        <v>82382</v>
+        <v>91052</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1312</v>
+        <v>1506</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -722,10 +722,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>666877</v>
+        <v>666865</v>
       </c>
       <c r="R2" t="n">
-        <v>7281408</v>
+        <v>7281403</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -785,10 +785,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121185919</v>
+        <v>121185989</v>
       </c>
       <c r="B3" t="n">
-        <v>90687</v>
+        <v>90715</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -801,21 +801,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -832,10 +832,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>666865</v>
+        <v>666823</v>
       </c>
       <c r="R3" t="n">
-        <v>7281403</v>
+        <v>7281386</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -895,10 +895,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121185989</v>
+        <v>121185975</v>
       </c>
       <c r="B4" t="n">
-        <v>90705</v>
+        <v>90693</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -911,21 +911,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -942,10 +942,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>666823</v>
+        <v>666850</v>
       </c>
       <c r="R4" t="n">
-        <v>7281386</v>
+        <v>7281361</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1005,10 +1005,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121185854</v>
+        <v>121185919</v>
       </c>
       <c r="B5" t="n">
-        <v>91042</v>
+        <v>90697</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1017,25 +1017,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1506</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1115,10 +1115,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121185975</v>
+        <v>121185794</v>
       </c>
       <c r="B6" t="n">
-        <v>90683</v>
+        <v>82385</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1131,21 +1131,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1108</v>
+        <v>1312</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1162,10 +1162,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>666850</v>
+        <v>666877</v>
       </c>
       <c r="R6" t="n">
-        <v>7281361</v>
+        <v>7281408</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1228,7 +1228,7 @@
         <v>121185959</v>
       </c>
       <c r="B7" t="n">
-        <v>78598</v>
+        <v>78601</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>

--- a/artfynd/A 20593-2024 artfynd.xlsx
+++ b/artfynd/A 20593-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121185854</v>
+        <v>121185959</v>
       </c>
       <c r="B2" t="n">
-        <v>91052</v>
+        <v>78601</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,31 +687,31 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1506</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -722,10 +722,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>666865</v>
+        <v>666850</v>
       </c>
       <c r="R2" t="n">
-        <v>7281403</v>
+        <v>7281398</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -785,10 +785,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121185989</v>
+        <v>121185854</v>
       </c>
       <c r="B3" t="n">
-        <v>90715</v>
+        <v>91052</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,25 +797,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>1506</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -832,10 +832,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>666823</v>
+        <v>666865</v>
       </c>
       <c r="R3" t="n">
-        <v>7281386</v>
+        <v>7281403</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -895,10 +895,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121185975</v>
+        <v>121185794</v>
       </c>
       <c r="B4" t="n">
-        <v>90693</v>
+        <v>82385</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -911,21 +911,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1108</v>
+        <v>1312</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -942,10 +942,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>666850</v>
+        <v>666877</v>
       </c>
       <c r="R4" t="n">
-        <v>7281361</v>
+        <v>7281408</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1115,10 +1115,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121185794</v>
+        <v>121185989</v>
       </c>
       <c r="B6" t="n">
-        <v>82385</v>
+        <v>90715</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1131,21 +1131,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1312</v>
+        <v>5432</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1162,10 +1162,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>666877</v>
+        <v>666823</v>
       </c>
       <c r="R6" t="n">
-        <v>7281408</v>
+        <v>7281386</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1225,10 +1225,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121185959</v>
+        <v>121185975</v>
       </c>
       <c r="B7" t="n">
-        <v>78601</v>
+        <v>90693</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1241,27 +1241,27 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
@@ -1275,7 +1275,7 @@
         <v>666850</v>
       </c>
       <c r="R7" t="n">
-        <v>7281398</v>
+        <v>7281361</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>

--- a/artfynd/A 20593-2024 artfynd.xlsx
+++ b/artfynd/A 20593-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121185959</v>
+        <v>121185975</v>
       </c>
       <c r="B2" t="n">
-        <v>78601</v>
+        <v>90705</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,27 +691,27 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -725,7 +725,7 @@
         <v>666850</v>
       </c>
       <c r="R2" t="n">
-        <v>7281398</v>
+        <v>7281361</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -785,10 +785,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121185854</v>
+        <v>121185919</v>
       </c>
       <c r="B3" t="n">
-        <v>91052</v>
+        <v>90709</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,25 +797,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1506</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -895,10 +895,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121185794</v>
+        <v>121185989</v>
       </c>
       <c r="B4" t="n">
-        <v>82385</v>
+        <v>90727</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -911,21 +911,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1312</v>
+        <v>5432</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -942,10 +942,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>666877</v>
+        <v>666823</v>
       </c>
       <c r="R4" t="n">
-        <v>7281408</v>
+        <v>7281386</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1005,10 +1005,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121185919</v>
+        <v>121185794</v>
       </c>
       <c r="B5" t="n">
-        <v>90697</v>
+        <v>82388</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1021,21 +1021,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>1312</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1052,10 +1052,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>666865</v>
+        <v>666877</v>
       </c>
       <c r="R5" t="n">
-        <v>7281403</v>
+        <v>7281408</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1115,10 +1115,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121185989</v>
+        <v>121185854</v>
       </c>
       <c r="B6" t="n">
-        <v>90715</v>
+        <v>91064</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1127,25 +1127,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>1506</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1162,10 +1162,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>666823</v>
+        <v>666865</v>
       </c>
       <c r="R6" t="n">
-        <v>7281386</v>
+        <v>7281403</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1225,10 +1225,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121185975</v>
+        <v>121185959</v>
       </c>
       <c r="B7" t="n">
-        <v>90693</v>
+        <v>78604</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1241,27 +1241,27 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
@@ -1275,7 +1275,7 @@
         <v>666850</v>
       </c>
       <c r="R7" t="n">
-        <v>7281361</v>
+        <v>7281398</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>

--- a/artfynd/A 20593-2024 artfynd.xlsx
+++ b/artfynd/A 20593-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121185975</v>
+        <v>121185854</v>
       </c>
       <c r="B2" t="n">
-        <v>90705</v>
+        <v>91065</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1108</v>
+        <v>1506</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -722,10 +722,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>666850</v>
+        <v>666865</v>
       </c>
       <c r="R2" t="n">
-        <v>7281361</v>
+        <v>7281403</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -785,10 +785,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121185919</v>
+        <v>121185975</v>
       </c>
       <c r="B3" t="n">
-        <v>90709</v>
+        <v>90706</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -801,21 +801,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -832,10 +832,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>666865</v>
+        <v>666850</v>
       </c>
       <c r="R3" t="n">
-        <v>7281403</v>
+        <v>7281361</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -895,10 +895,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121185989</v>
+        <v>121185794</v>
       </c>
       <c r="B4" t="n">
-        <v>90727</v>
+        <v>82388</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -911,21 +911,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>1312</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -942,10 +942,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>666823</v>
+        <v>666877</v>
       </c>
       <c r="R4" t="n">
-        <v>7281386</v>
+        <v>7281408</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1005,10 +1005,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121185794</v>
+        <v>121185959</v>
       </c>
       <c r="B5" t="n">
-        <v>82388</v>
+        <v>78604</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1021,27 +1021,27 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
@@ -1052,10 +1052,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>666877</v>
+        <v>666850</v>
       </c>
       <c r="R5" t="n">
-        <v>7281408</v>
+        <v>7281398</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1115,10 +1115,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121185854</v>
+        <v>121185919</v>
       </c>
       <c r="B6" t="n">
-        <v>91064</v>
+        <v>90710</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1127,25 +1127,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1506</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1225,10 +1225,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121185959</v>
+        <v>121185989</v>
       </c>
       <c r="B7" t="n">
-        <v>78604</v>
+        <v>90728</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1241,27 +1241,27 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>666850</v>
+        <v>666823</v>
       </c>
       <c r="R7" t="n">
-        <v>7281398</v>
+        <v>7281386</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>

--- a/artfynd/A 20593-2024 artfynd.xlsx
+++ b/artfynd/A 20593-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121185854</v>
+        <v>121185959</v>
       </c>
       <c r="B2" t="n">
-        <v>91065</v>
+        <v>78607</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,31 +687,31 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1506</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -722,10 +722,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>666865</v>
+        <v>666850</v>
       </c>
       <c r="R2" t="n">
-        <v>7281403</v>
+        <v>7281398</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -785,10 +785,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121185975</v>
+        <v>121185919</v>
       </c>
       <c r="B3" t="n">
-        <v>90706</v>
+        <v>90713</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -801,21 +801,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1108</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -832,10 +832,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>666850</v>
+        <v>666865</v>
       </c>
       <c r="R3" t="n">
-        <v>7281361</v>
+        <v>7281403</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -895,10 +895,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121185794</v>
+        <v>121185854</v>
       </c>
       <c r="B4" t="n">
-        <v>82388</v>
+        <v>91068</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -907,25 +907,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1312</v>
+        <v>1506</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -942,10 +942,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>666877</v>
+        <v>666865</v>
       </c>
       <c r="R4" t="n">
-        <v>7281408</v>
+        <v>7281403</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1005,10 +1005,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121185959</v>
+        <v>121185794</v>
       </c>
       <c r="B5" t="n">
-        <v>78604</v>
+        <v>82391</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1021,27 +1021,27 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
@@ -1052,10 +1052,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>666850</v>
+        <v>666877</v>
       </c>
       <c r="R5" t="n">
-        <v>7281398</v>
+        <v>7281408</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1115,10 +1115,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121185919</v>
+        <v>121185989</v>
       </c>
       <c r="B6" t="n">
-        <v>90710</v>
+        <v>90731</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1131,21 +1131,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1162,10 +1162,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>666865</v>
+        <v>666823</v>
       </c>
       <c r="R6" t="n">
-        <v>7281403</v>
+        <v>7281386</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1225,10 +1225,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121185989</v>
+        <v>121185975</v>
       </c>
       <c r="B7" t="n">
-        <v>90728</v>
+        <v>90709</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1241,21 +1241,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>666823</v>
+        <v>666850</v>
       </c>
       <c r="R7" t="n">
-        <v>7281386</v>
+        <v>7281361</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>

--- a/artfynd/A 20593-2024 artfynd.xlsx
+++ b/artfynd/A 20593-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121185959</v>
+        <v>121185989</v>
       </c>
       <c r="B2" t="n">
-        <v>78607</v>
+        <v>90731</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,27 +691,27 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -722,10 +722,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>666850</v>
+        <v>666823</v>
       </c>
       <c r="R2" t="n">
-        <v>7281398</v>
+        <v>7281386</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -895,10 +895,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121185854</v>
+        <v>121185794</v>
       </c>
       <c r="B4" t="n">
-        <v>91068</v>
+        <v>82391</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -907,25 +907,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1506</v>
+        <v>1312</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -942,10 +942,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>666865</v>
+        <v>666877</v>
       </c>
       <c r="R4" t="n">
-        <v>7281403</v>
+        <v>7281408</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1005,10 +1005,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121185794</v>
+        <v>121185854</v>
       </c>
       <c r="B5" t="n">
-        <v>82391</v>
+        <v>91068</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1017,25 +1017,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1312</v>
+        <v>1506</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1052,10 +1052,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>666877</v>
+        <v>666865</v>
       </c>
       <c r="R5" t="n">
-        <v>7281408</v>
+        <v>7281403</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1115,10 +1115,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121185989</v>
+        <v>121185975</v>
       </c>
       <c r="B6" t="n">
-        <v>90731</v>
+        <v>90709</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1131,21 +1131,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1162,10 +1162,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>666823</v>
+        <v>666850</v>
       </c>
       <c r="R6" t="n">
-        <v>7281386</v>
+        <v>7281361</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1225,10 +1225,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121185975</v>
+        <v>121185959</v>
       </c>
       <c r="B7" t="n">
-        <v>90709</v>
+        <v>78607</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1241,27 +1241,27 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
@@ -1275,7 +1275,7 @@
         <v>666850</v>
       </c>
       <c r="R7" t="n">
-        <v>7281361</v>
+        <v>7281398</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>

--- a/artfynd/A 20593-2024 artfynd.xlsx
+++ b/artfynd/A 20593-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121185989</v>
+        <v>121185794</v>
       </c>
       <c r="B2" t="n">
-        <v>90731</v>
+        <v>82392</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>1312</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -722,10 +722,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>666823</v>
+        <v>666877</v>
       </c>
       <c r="R2" t="n">
-        <v>7281386</v>
+        <v>7281408</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -785,10 +785,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121185919</v>
+        <v>121185959</v>
       </c>
       <c r="B3" t="n">
-        <v>90713</v>
+        <v>78608</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -801,27 +801,27 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -832,10 +832,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>666865</v>
+        <v>666850</v>
       </c>
       <c r="R3" t="n">
-        <v>7281403</v>
+        <v>7281398</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -895,10 +895,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121185794</v>
+        <v>121185854</v>
       </c>
       <c r="B4" t="n">
-        <v>82391</v>
+        <v>91074</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -907,25 +907,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1312</v>
+        <v>1506</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -942,10 +942,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>666877</v>
+        <v>666865</v>
       </c>
       <c r="R4" t="n">
-        <v>7281408</v>
+        <v>7281403</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1005,10 +1005,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121185854</v>
+        <v>121185919</v>
       </c>
       <c r="B5" t="n">
-        <v>91068</v>
+        <v>90719</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1017,25 +1017,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1506</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1118,7 +1118,7 @@
         <v>121185975</v>
       </c>
       <c r="B6" t="n">
-        <v>90709</v>
+        <v>90715</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1225,10 +1225,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121185959</v>
+        <v>121185989</v>
       </c>
       <c r="B7" t="n">
-        <v>78607</v>
+        <v>90737</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1241,27 +1241,27 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>666850</v>
+        <v>666823</v>
       </c>
       <c r="R7" t="n">
-        <v>7281398</v>
+        <v>7281386</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
